--- a/PRODUCTOS ELITE.xlsx
+++ b/PRODUCTOS ELITE.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Elite Medical\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rafajime/Documents/landing-page-hero/landing-page-hero/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF29DDA-CEAD-2747-9858-626E975E5BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -379,7 +378,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -497,15 +496,6 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -522,6 +512,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,62 +800,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:K48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" customWidth="1"/>
-    <col min="5" max="5" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.140625" customWidth="1"/>
-    <col min="9" max="9" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" customWidth="1"/>
+    <col min="9" max="9" width="48.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="1" t="s">
+    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:11" ht="22" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="E4" s="1" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="I4" s="1" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="I4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" spans="1:11" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="I5" s="4" t="s">
+      <c r="G5" s="3"/>
+      <c r="I5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -876,7 +875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -896,7 +895,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -916,7 +915,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -936,7 +935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -956,7 +955,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
         <v>30</v>
       </c>
@@ -970,7 +969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
         <v>33</v>
       </c>
@@ -984,7 +983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
         <v>33</v>
       </c>
@@ -998,7 +997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
         <v>38</v>
       </c>
@@ -1012,7 +1011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E15" t="s">
         <v>42</v>
       </c>
@@ -1026,7 +1025,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E16" t="s">
         <v>46</v>
       </c>
@@ -1040,7 +1039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
         <v>50</v>
       </c>
@@ -1054,14 +1053,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
         <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I18" t="s">
@@ -1071,18 +1070,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="5"/>
       <c r="E19" t="s">
         <v>56</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="9"/>
+      <c r="G19" s="6"/>
       <c r="I19" t="s">
         <v>57</v>
       </c>
@@ -1090,7 +1089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -1103,7 +1102,7 @@
       <c r="F20" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="9"/>
+      <c r="G20" s="6"/>
       <c r="I20" t="s">
         <v>60</v>
       </c>
@@ -1111,7 +1110,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -1121,7 +1120,7 @@
       <c r="F21" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="9"/>
+      <c r="G21" s="6"/>
       <c r="I21" t="s">
         <v>63</v>
       </c>
@@ -1129,7 +1128,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -1142,7 +1141,7 @@
       <c r="F22" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="9"/>
+      <c r="G22" s="6"/>
       <c r="I22" t="s">
         <v>66</v>
       </c>
@@ -1150,7 +1149,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -1163,7 +1162,7 @@
       <c r="F23" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="9"/>
+      <c r="G23" s="6"/>
       <c r="I23" t="s">
         <v>69</v>
       </c>
@@ -1171,7 +1170,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -1184,7 +1183,7 @@
       <c r="F24" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I24" t="s">
@@ -1194,7 +1193,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>73</v>
       </c>
@@ -1204,7 +1203,7 @@
       <c r="F25" t="s">
         <v>28</v>
       </c>
-      <c r="G25" s="9"/>
+      <c r="G25" s="6"/>
       <c r="I25" t="s">
         <v>75</v>
       </c>
@@ -1212,7 +1211,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -1225,7 +1224,7 @@
       <c r="F26" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="9"/>
+      <c r="G26" s="6"/>
       <c r="I26" t="s">
         <v>78</v>
       </c>
@@ -1233,7 +1232,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -1246,7 +1245,7 @@
       <c r="F27" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="9"/>
+      <c r="G27" s="6"/>
       <c r="I27" t="s">
         <v>82</v>
       </c>
@@ -1254,7 +1253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -1264,7 +1263,7 @@
       <c r="F28" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="6" t="s">
         <v>53</v>
       </c>
       <c r="I28" t="s">
@@ -1274,14 +1273,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>86</v>
       </c>
       <c r="B29" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="9"/>
+      <c r="G29" s="6"/>
       <c r="I29" t="s">
         <v>87</v>
       </c>
@@ -1289,7 +1288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>88</v>
       </c>
@@ -1297,17 +1296,17 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -1315,7 +1314,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -1323,24 +1322,24 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="I35" s="1" t="s">
+    <row r="35" spans="1:11" ht="22" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I35" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="1" t="s">
+      <c r="J35" s="8"/>
+      <c r="K35" s="9"/>
+    </row>
+    <row r="36" spans="1:11" ht="22" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
-      <c r="E36" s="1" t="s">
+      <c r="B36" s="8"/>
+      <c r="C36" s="9"/>
+      <c r="E36" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="3"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="9"/>
       <c r="I36" t="s">
         <v>94</v>
       </c>
@@ -1348,18 +1347,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:11" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="E37" s="4" t="s">
+      <c r="C37" s="3"/>
+      <c r="E37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I37" t="s">
@@ -1369,7 +1368,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -1389,7 +1388,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -1423,7 +1422,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -1436,11 +1435,11 @@
       <c r="I41" t="s">
         <v>112</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>29</v>
       </c>
@@ -1454,7 +1453,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1476,7 +1475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1484,7 +1483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>41</v>
       </c>
@@ -1492,7 +1491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1500,7 +1499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1518,23 +1517,15 @@
     <mergeCell ref="E36:G36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - Oracle Restricted \Employees Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{825c952f-1947-4719-99e7-7bc5a76060a8}" enabled="1" method="Standard" siteId="{4e2c6054-71cb-48f1-bd6c-3a9705aca71b}" contentBits="3" removed="0"/>
+</clbl:labelList>
 </file>